--- a/FlightRisk/CustomerPrepayment.xlsx
+++ b/FlightRisk/CustomerPrepayment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leo/Github/XeroAPI/FlightRisk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BED8E2-18B5-974C-B872-E8F78ABB6C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEA39AF-53AD-4247-B9F1-2A9F50A0DCF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9700" yWindow="-22820" windowWidth="27640" windowHeight="16520" xr2:uid="{38D5C541-7871-704C-ADD3-7E7071C154A8}"/>
+    <workbookView xWindow="6560" yWindow="-20980" windowWidth="27640" windowHeight="16520" xr2:uid="{38D5C541-7871-704C-ADD3-7E7071C154A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>Sales Order Number</t>
   </si>
@@ -47,25 +47,136 @@
     <t>Prepayment $</t>
   </si>
   <si>
-    <t>FRC#2637</t>
-  </si>
-  <si>
-    <t>FRC#3130</t>
-  </si>
-  <si>
     <t>FRC#3194</t>
   </si>
   <si>
-    <t>FRC#3197</t>
-  </si>
-  <si>
-    <t>SI-00000547</t>
-  </si>
-  <si>
-    <t>SI-00000580</t>
-  </si>
-  <si>
-    <t>FRC#3917</t>
+    <t>FRC#3444</t>
+  </si>
+  <si>
+    <t>FRC#3499</t>
+  </si>
+  <si>
+    <t>FRC#3548</t>
+  </si>
+  <si>
+    <t>FRC#3549</t>
+  </si>
+  <si>
+    <t>FRC#3585</t>
+  </si>
+  <si>
+    <t>FRC#3615</t>
+  </si>
+  <si>
+    <t>FRC#3617</t>
+  </si>
+  <si>
+    <t>FRC#3626</t>
+  </si>
+  <si>
+    <t>FRC#3627</t>
+  </si>
+  <si>
+    <t>FRC#3636</t>
+  </si>
+  <si>
+    <t>FRC#3641</t>
+  </si>
+  <si>
+    <t>FRC#3649</t>
+  </si>
+  <si>
+    <t>FRC#3651</t>
+  </si>
+  <si>
+    <t>FRC#3657</t>
+  </si>
+  <si>
+    <t>FRC#3659</t>
+  </si>
+  <si>
+    <t>FRC#3661</t>
+  </si>
+  <si>
+    <t>FRC#3662</t>
+  </si>
+  <si>
+    <t>FRC#3663</t>
+  </si>
+  <si>
+    <t>FRC#3675</t>
+  </si>
+  <si>
+    <t>FRC#3676</t>
+  </si>
+  <si>
+    <t>FRC#3678</t>
+  </si>
+  <si>
+    <t>FRC#3680</t>
+  </si>
+  <si>
+    <t>FRC#3683</t>
+  </si>
+  <si>
+    <t>FRC#3684</t>
+  </si>
+  <si>
+    <t>FRC#3686</t>
+  </si>
+  <si>
+    <t>FRC#3688</t>
+  </si>
+  <si>
+    <t>FRC#3698</t>
+  </si>
+  <si>
+    <t>FRC#3702</t>
+  </si>
+  <si>
+    <t>FRC#3704</t>
+  </si>
+  <si>
+    <t>FRC#3716</t>
+  </si>
+  <si>
+    <t>FRC#3747</t>
+  </si>
+  <si>
+    <t>SI-00000694</t>
+  </si>
+  <si>
+    <t>SI-00000734</t>
+  </si>
+  <si>
+    <t>SI-00000738</t>
+  </si>
+  <si>
+    <t>SI-00000751</t>
+  </si>
+  <si>
+    <t>SI-00000752</t>
+  </si>
+  <si>
+    <t>SI-00000753</t>
+  </si>
+  <si>
+    <t>SI-00000754</t>
+  </si>
+  <si>
+    <t>SI-00000755</t>
+  </si>
+  <si>
+    <t>SI-00000771</t>
+  </si>
+  <si>
+    <t>SI-00000807</t>
+  </si>
+  <si>
+    <t>SI-00000808</t>
+  </si>
+  <si>
+    <t>SI-00000809</t>
   </si>
 </sst>
 </file>
@@ -454,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43792BBA-C766-5C40-9C57-A0361E6015E8}">
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -473,10 +584,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>45990</v>
+        <v>46020</v>
       </c>
       <c r="C2" s="4">
-        <v>4508.99</v>
+        <v>11635.98</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -484,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>46017</v>
+        <v>46037</v>
       </c>
       <c r="C3" s="4">
-        <v>4248.99</v>
+        <v>2958.98</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -495,10 +606,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>46020</v>
+        <v>46042</v>
       </c>
       <c r="C4" s="4">
-        <v>11635.98</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -506,229 +617,451 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>46022</v>
-      </c>
-      <c r="C5" s="2">
-        <v>799</v>
+        <v>46043</v>
+      </c>
+      <c r="C5" s="4">
+        <v>3983.99</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>46021</v>
-      </c>
-      <c r="C6" s="2">
-        <v>-799</v>
+        <v>46043</v>
+      </c>
+      <c r="C6" s="4">
+        <v>4399</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>46013</v>
+        <v>46045</v>
       </c>
       <c r="C7" s="4">
-        <v>20242.47</v>
+        <v>2848.99</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3">
-        <v>46020</v>
-      </c>
-      <c r="C8" s="4">
-        <v>11021.99</v>
+        <v>46049</v>
+      </c>
+      <c r="C8" s="2">
+        <v>294.95999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46050</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2799</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46050</v>
+      </c>
+      <c r="C10" s="2">
+        <v>259.98</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46050</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2579.09</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46050</v>
+      </c>
+      <c r="C12" s="4">
+        <v>3983.99</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C13" s="4">
+        <v>3333.23</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C14" s="2">
+        <v>149.99</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2783.99</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1999</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
+      <c r="A17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2783.99</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
+      <c r="A18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2916.99</v>
+      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
+      <c r="A19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2399</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
+      <c r="A20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C20" s="4">
+        <v>4048.99</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
+      <c r="A21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C21" s="4">
+        <v>3999</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
+      <c r="A22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2798.99</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
+      <c r="A23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C23" s="2">
+        <v>79.989999999999995</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
+      <c r="A24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="3">
+        <v>46053</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1999</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
+      <c r="A25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3999</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
+      <c r="A26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C26" s="4">
+        <v>3608.99</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
+      <c r="A27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C27" s="4">
+        <v>3499</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
+      <c r="A28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C28" s="4">
+        <v>3999</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
+      <c r="A29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="3">
+        <v>46050</v>
+      </c>
+      <c r="C29" s="4">
+        <v>2699</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="2"/>
+      <c r="A30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C30" s="4">
+        <v>4083.99</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
+      <c r="A31" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="3">
+        <v>46049</v>
+      </c>
+      <c r="C31" s="4">
+        <v>4373.96</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
+      <c r="A32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="3">
+        <v>46052</v>
+      </c>
+      <c r="C32" s="4">
+        <v>4248.9799999999996</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="4"/>
+      <c r="A33" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="3">
+        <v>46053</v>
+      </c>
+      <c r="C33" s="4">
+        <v>2699</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="2"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="4"/>
+      <c r="A34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="3">
+        <v>46041</v>
+      </c>
+      <c r="C34" s="4">
+        <v>10722.76</v>
+      </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4"/>
+      <c r="A35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="3">
+        <v>46048</v>
+      </c>
+      <c r="C35" s="4">
+        <v>7047.75</v>
+      </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="4"/>
+      <c r="A36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="3">
+        <v>46048</v>
+      </c>
+      <c r="C36" s="4">
+        <v>9071.98</v>
+      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="4"/>
+      <c r="A37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="3">
+        <v>46050</v>
+      </c>
+      <c r="C37" s="4">
+        <v>23390.22</v>
+      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="2"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="4"/>
+      <c r="A38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="3">
+        <v>46050</v>
+      </c>
+      <c r="C38" s="4">
+        <v>2999.25</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="4"/>
+      <c r="A39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="3">
+        <v>46050</v>
+      </c>
+      <c r="C39" s="4">
+        <v>2999.25</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="4"/>
+      <c r="A40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="3">
+        <v>46050</v>
+      </c>
+      <c r="C40" s="4">
+        <v>2999.25</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="2"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="4"/>
+      <c r="A41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="3">
+        <v>46050</v>
+      </c>
+      <c r="C41" s="4">
+        <v>7047.74</v>
+      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="4"/>
+      <c r="A42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="3">
+        <v>46052</v>
+      </c>
+      <c r="C42" s="4">
+        <v>8226</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="2"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="4"/>
+      <c r="A43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="3">
+        <v>46053</v>
+      </c>
+      <c r="C43" s="4">
+        <v>1499.25</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="2"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="4"/>
+      <c r="A44" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="3">
+        <v>46053</v>
+      </c>
+      <c r="C44" s="4">
+        <v>4497.75</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="4"/>
+      <c r="A45" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="3">
+        <v>46051</v>
+      </c>
+      <c r="C45" s="4">
+        <v>2999.25</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
@@ -743,12 +1076,12 @@
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
-      <c r="C48" s="4"/>
+      <c r="C48" s="2"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
-      <c r="C49" s="4"/>
+      <c r="C49" s="2"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
@@ -763,12 +1096,12 @@
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
-      <c r="C52" s="2"/>
+      <c r="C52" s="4"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
-      <c r="C53" s="2"/>
+      <c r="C53" s="4"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
@@ -828,7 +1161,7 @@
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
-      <c r="C65" s="4"/>
+      <c r="C65" s="2"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
@@ -838,7 +1171,7 @@
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
-      <c r="C67" s="2"/>
+      <c r="C67" s="4"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
@@ -898,7 +1231,7 @@
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
-      <c r="C79" s="4"/>
+      <c r="C79" s="2"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
@@ -908,7 +1241,7 @@
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
-      <c r="C81" s="2"/>
+      <c r="C81" s="4"/>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
@@ -943,7 +1276,7 @@
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
-      <c r="C88" s="4"/>
+      <c r="C88" s="2"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
@@ -953,17 +1286,7 @@
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
-      <c r="C90" s="2"/>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91" s="2"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="4"/>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A92" s="2"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="4"/>
+      <c r="C90" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/FlightRisk/CustomerPrepayment.xlsx
+++ b/FlightRisk/CustomerPrepayment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TRIHALO\XeroAPI\FlightRisk\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trihalocomau.sharepoint.com/sites/Trihalo/Shared Documents/Clients/FlightRisk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7C019C-6C41-479D-9BF3-CB40787F63E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{9B7C019C-6C41-479D-9BF3-CB40787F63E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04E8DAF2-FD91-B949-93E2-C16A43839A40}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2190" windowWidth="28800" windowHeight="18810" xr2:uid="{38D5C541-7871-704C-ADD3-7E7071C154A8}"/>
+    <workbookView xWindow="2740" yWindow="2200" windowWidth="28800" windowHeight="18820" xr2:uid="{38D5C541-7871-704C-ADD3-7E7071C154A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Sales Order Number</t>
   </si>
@@ -50,7 +50,37 @@
     <t>FRC#3194</t>
   </si>
   <si>
-    <t>FRC#4500</t>
+    <t>FRC#3716</t>
+  </si>
+  <si>
+    <t>FRC#3747</t>
+  </si>
+  <si>
+    <t>FRC#3798</t>
+  </si>
+  <si>
+    <t>FRC#3804</t>
+  </si>
+  <si>
+    <t>FRC#3830</t>
+  </si>
+  <si>
+    <t>FRC#3861</t>
+  </si>
+  <si>
+    <t>FRC#4040</t>
+  </si>
+  <si>
+    <t>FRC#4081</t>
+  </si>
+  <si>
+    <t>SI-00000734</t>
+  </si>
+  <si>
+    <t>SI-00000902</t>
+  </si>
+  <si>
+    <t>SI-00000916</t>
   </si>
 </sst>
 </file>
@@ -440,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43792BBA-C766-5C40-9C57-A0361E6015E8}">
   <dimension ref="A1:C90"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,7 +483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -464,448 +494,508 @@
         <v>11635.98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>46081</v>
+        <v>46052</v>
       </c>
       <c r="C3" s="4">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4248.9799999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46053</v>
+      </c>
+      <c r="C4" s="4">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46056</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46058</v>
+      </c>
+      <c r="C6" s="2">
+        <v>179.98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46062</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2953.96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46064</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2883.98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46078</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46080</v>
+      </c>
+      <c r="C10" s="4">
+        <v>4198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46048</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46070</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2024.24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46070</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2024.24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
+      <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="4"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="4"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="4"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="4"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="4"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="4"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="4"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="4"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="4"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="4"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="4"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="4"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="4"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="4"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="C45" s="4"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="C46" s="4"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="C47" s="4"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" s="2"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" s="2"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="2"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="4"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="4"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="4"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="4"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="4"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="4"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="4"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="4"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="4"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="4"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="4"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="4"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="4"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="2"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="4"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="4"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="4"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="4"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="4"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="4"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" s="4"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="4"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" s="4"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="4"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" s="4"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="4"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" s="4"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" s="4"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="4"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" s="4"/>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="4"/>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="4"/>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="4"/>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="4"/>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="4"/>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="2"/>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="4"/>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="4"/>
@@ -913,4 +1003,323 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="29d34c63-b11d-471e-b329-ad4718a72bd9" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1764877c-90cb-4e8e-814f-83a0304c7599">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010037A4F1C30EC86C4C91373B3A62F2174F" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d0c8250cbc4d9747c928a14a1c9fdc6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1764877c-90cb-4e8e-814f-83a0304c7599" xmlns:ns3="29d34c63-b11d-471e-b329-ad4718a72bd9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a6abafa92a2a8b7fc26b8ac3f987cc62" ns2:_="" ns3:_="">
+    <xsd:import namespace="1764877c-90cb-4e8e-814f-83a0304c7599"/>
+    <xsd:import namespace="29d34c63-b11d-471e-b329-ad4718a72bd9"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1764877c-90cb-4e8e-814f-83a0304c7599" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9d12fb58-da32-4f30-8c31-ac53df30d788" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="29d34c63-b11d-471e-b329-ad4718a72bd9" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{955c3b38-dfbd-459f-ac00-b580526e310f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="29d34c63-b11d-471e-b329-ad4718a72bd9">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BED873C-C9EE-4B4F-B012-95CE561B9FDE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="29d34c63-b11d-471e-b329-ad4718a72bd9"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="1764877c-90cb-4e8e-814f-83a0304c7599"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DA931E2-1B65-4BFA-BC64-8B1017E5CE8A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF84C396-305B-42CF-91E7-A86065F4EAAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1764877c-90cb-4e8e-814f-83a0304c7599"/>
+    <ds:schemaRef ds:uri="29d34c63-b11d-471e-b329-ad4718a72bd9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/FlightRisk/CustomerPrepayment.xlsx
+++ b/FlightRisk/CustomerPrepayment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leo/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46903E76-12F4-324B-AC40-70D0FB31F26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23AE8F5D-2D73-6249-8004-AA68DCBF9530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3080" yWindow="2180" windowWidth="28040" windowHeight="17180" xr2:uid="{61119ABA-6E25-8044-BA20-282A1BE9BE1B}"/>
+    <workbookView xWindow="3080" yWindow="2200" windowWidth="28040" windowHeight="17180" xr2:uid="{7D392A50-0562-E043-9B49-D03505D333CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>Sales Order Number</t>
   </si>
@@ -53,12 +53,6 @@
     <t>FRC#0000</t>
   </si>
   <si>
-    <t>FRC#4748</t>
-  </si>
-  <si>
-    <t>FRC#4840</t>
-  </si>
-  <si>
     <t>FRC#4949</t>
   </si>
   <si>
@@ -113,13 +107,124 @@
     <t>FRC#5262</t>
   </si>
   <si>
-    <t>FRC#5286</t>
-  </si>
-  <si>
-    <t>FRC#5299</t>
-  </si>
-  <si>
-    <t>FRC#5317</t>
+    <t>FRC#5350</t>
+  </si>
+  <si>
+    <t>FRC#5391</t>
+  </si>
+  <si>
+    <t>FRC#5393</t>
+  </si>
+  <si>
+    <t>FRC#5405</t>
+  </si>
+  <si>
+    <t>FRC#5411</t>
+  </si>
+  <si>
+    <t>FRC#5417</t>
+  </si>
+  <si>
+    <t>FRC#5418</t>
+  </si>
+  <si>
+    <t>FRC#5444</t>
+  </si>
+  <si>
+    <t>FRC#5450</t>
+  </si>
+  <si>
+    <t>FRC#5458</t>
+  </si>
+  <si>
+    <t>FRC#5459</t>
+  </si>
+  <si>
+    <t>FRC#5462</t>
+  </si>
+  <si>
+    <t>FRC#5468</t>
+  </si>
+  <si>
+    <t>FRC#5470</t>
+  </si>
+  <si>
+    <t>FRC#5474</t>
+  </si>
+  <si>
+    <t>FRC#5475</t>
+  </si>
+  <si>
+    <t>FRC#5507</t>
+  </si>
+  <si>
+    <t>FRC#5521</t>
+  </si>
+  <si>
+    <t>FRC#5527</t>
+  </si>
+  <si>
+    <t>FRC#5540</t>
+  </si>
+  <si>
+    <t>FRC#5545</t>
+  </si>
+  <si>
+    <t>FRC#5546</t>
+  </si>
+  <si>
+    <t>FRC#5547</t>
+  </si>
+  <si>
+    <t>FRC#5592</t>
+  </si>
+  <si>
+    <t>FRC#5595</t>
+  </si>
+  <si>
+    <t>FRC#5603</t>
+  </si>
+  <si>
+    <t>FRC#5608</t>
+  </si>
+  <si>
+    <t>FRC#5616</t>
+  </si>
+  <si>
+    <t>FRC#5630</t>
+  </si>
+  <si>
+    <t>FRC#5631</t>
+  </si>
+  <si>
+    <t>FRC#5632</t>
+  </si>
+  <si>
+    <t>FRC#5646</t>
+  </si>
+  <si>
+    <t>FRC#5675</t>
+  </si>
+  <si>
+    <t>FRC#5694</t>
+  </si>
+  <si>
+    <t>FRC#5697</t>
+  </si>
+  <si>
+    <t>FRC#5698</t>
+  </si>
+  <si>
+    <t>FRC#5706</t>
+  </si>
+  <si>
+    <t>FRC#5717</t>
+  </si>
+  <si>
+    <t>FRC#5719</t>
+  </si>
+  <si>
+    <t>FRC#5737</t>
   </si>
   <si>
     <t>SI-00001362</t>
@@ -140,16 +245,49 @@
     <t>SI-00001426</t>
   </si>
   <si>
-    <t>SI-00001511</t>
-  </si>
-  <si>
     <t>SI-00001521</t>
   </si>
   <si>
+    <t>SI-00001523</t>
+  </si>
+  <si>
     <t>SI-00001525</t>
   </si>
   <si>
     <t>SI-00001526</t>
+  </si>
+  <si>
+    <t>SI-00001527</t>
+  </si>
+  <si>
+    <t>SI-00001551</t>
+  </si>
+  <si>
+    <t>SI-00001558</t>
+  </si>
+  <si>
+    <t>SI-00001563</t>
+  </si>
+  <si>
+    <t>SI-00001586</t>
+  </si>
+  <si>
+    <t>SI-00001587</t>
+  </si>
+  <si>
+    <t>SI-00001588</t>
+  </si>
+  <si>
+    <t>SI-00001594</t>
+  </si>
+  <si>
+    <t>SI-00001614</t>
+  </si>
+  <si>
+    <t>SI-00001621</t>
+  </si>
+  <si>
+    <t>SI-00001630</t>
   </si>
   <si>
     <t>SI-00001643</t>
@@ -540,8 +678,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E88305E-AC5C-2849-BDC9-0FF361CC0A23}">
-  <dimension ref="A1:C36"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C282293D-E83B-DC4B-AEC7-DBFF19DFA17D}">
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -571,10 +709,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>46108</v>
-      </c>
-      <c r="C3" s="2">
-        <v>467.99</v>
+        <v>46121</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2699</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -582,10 +720,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>46113</v>
+        <v>46128</v>
       </c>
       <c r="C4" s="4">
-        <v>2967</v>
+        <v>2429.1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -593,10 +731,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>46121</v>
+        <v>46129</v>
       </c>
       <c r="C5" s="4">
-        <v>2699</v>
+        <v>2783.99</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -604,10 +742,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>46128</v>
-      </c>
-      <c r="C6" s="4">
-        <v>2429.1</v>
+        <v>46129</v>
+      </c>
+      <c r="C6" s="2">
+        <v>69.94</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -615,10 +753,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C7" s="4">
-        <v>2783.99</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -626,10 +764,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="3">
-        <v>46129</v>
-      </c>
-      <c r="C8" s="2">
-        <v>69.94</v>
+        <v>46132</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2943.97</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -637,10 +775,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="3">
-        <v>46132</v>
-      </c>
-      <c r="C9" s="4">
-        <v>1100</v>
+        <v>46133</v>
+      </c>
+      <c r="C9" s="2">
+        <v>49.99</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -648,10 +786,10 @@
         <v>11</v>
       </c>
       <c r="B10" s="3">
-        <v>46132</v>
+        <v>46128</v>
       </c>
       <c r="C10" s="4">
-        <v>2943.97</v>
+        <v>2783.99</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -659,10 +797,10 @@
         <v>12</v>
       </c>
       <c r="B11" s="3">
-        <v>46133</v>
-      </c>
-      <c r="C11" s="2">
-        <v>49.99</v>
+        <v>46130</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2818.98</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -670,10 +808,10 @@
         <v>13</v>
       </c>
       <c r="B12" s="3">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="C12" s="4">
-        <v>2783.99</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -681,10 +819,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3">
-        <v>46130</v>
+        <v>46134</v>
       </c>
       <c r="C13" s="4">
-        <v>2818.98</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -692,10 +830,10 @@
         <v>15</v>
       </c>
       <c r="B14" s="3">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C14" s="4">
-        <v>2599</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -703,7 +841,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="3">
-        <v>46134</v>
+        <v>46132</v>
       </c>
       <c r="C15" s="4">
         <v>2699</v>
@@ -714,10 +852,10 @@
         <v>17</v>
       </c>
       <c r="B16" s="3">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="C16" s="4">
-        <v>2699</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -725,7 +863,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="3">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="C17" s="4">
         <v>2699</v>
@@ -736,10 +874,10 @@
         <v>19</v>
       </c>
       <c r="B18" s="3">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="C18" s="4">
-        <v>3999</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -758,7 +896,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="3">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C20" s="4">
         <v>2699</v>
@@ -769,7 +907,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="3">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="C21" s="4">
         <v>2699</v>
@@ -780,10 +918,10 @@
         <v>23</v>
       </c>
       <c r="B22" s="3">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="C22" s="4">
-        <v>2699</v>
+        <v>2429.1</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -791,10 +929,10 @@
         <v>24</v>
       </c>
       <c r="B23" s="3">
-        <v>46137</v>
-      </c>
-      <c r="C23" s="2">
-        <v>69.94</v>
+        <v>46148</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2699</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -802,10 +940,10 @@
         <v>25</v>
       </c>
       <c r="B24" s="3">
-        <v>46141</v>
-      </c>
-      <c r="C24" s="2">
-        <v>69.94</v>
+        <v>46148</v>
+      </c>
+      <c r="C24" s="4">
+        <v>2699</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -813,10 +951,10 @@
         <v>26</v>
       </c>
       <c r="B25" s="3">
-        <v>46142</v>
-      </c>
-      <c r="C25" s="2">
-        <v>94.94</v>
+        <v>46148</v>
+      </c>
+      <c r="C25" s="4">
+        <v>4148.99</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -824,10 +962,10 @@
         <v>27</v>
       </c>
       <c r="B26" s="3">
-        <v>46124</v>
+        <v>46146</v>
       </c>
       <c r="C26" s="4">
-        <v>2024.25</v>
+        <v>2982.99</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -835,10 +973,10 @@
         <v>28</v>
       </c>
       <c r="B27" s="3">
-        <v>46128</v>
+        <v>46148</v>
       </c>
       <c r="C27" s="4">
-        <v>4192.4799999999996</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -846,10 +984,10 @@
         <v>29</v>
       </c>
       <c r="B28" s="3">
-        <v>46129</v>
+        <v>46148</v>
       </c>
       <c r="C28" s="4">
-        <v>3199.47</v>
+        <v>4148.99</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -857,10 +995,10 @@
         <v>30</v>
       </c>
       <c r="B29" s="3">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="C29" s="4">
-        <v>12000</v>
+        <v>4353.96</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -868,10 +1006,10 @@
         <v>31</v>
       </c>
       <c r="B30" s="3">
-        <v>46130</v>
+        <v>46153</v>
       </c>
       <c r="C30" s="4">
-        <v>8997.75</v>
+        <v>3142.97</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -879,10 +1017,10 @@
         <v>32</v>
       </c>
       <c r="B31" s="3">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="C31" s="4">
-        <v>11021.99</v>
+        <v>2893.98</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -890,10 +1028,10 @@
         <v>33</v>
       </c>
       <c r="B32" s="3">
-        <v>46127</v>
+        <v>46154</v>
       </c>
       <c r="C32" s="4">
-        <v>1654</v>
+        <v>2808.99</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -901,10 +1039,10 @@
         <v>34</v>
       </c>
       <c r="B33" s="3">
-        <v>46140</v>
+        <v>46155</v>
       </c>
       <c r="C33" s="4">
-        <v>4083.99</v>
+        <v>2564.08</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -912,10 +1050,10 @@
         <v>35</v>
       </c>
       <c r="B34" s="3">
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="C34" s="4">
-        <v>2783.99</v>
+        <v>2843.98</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -923,10 +1061,10 @@
         <v>36</v>
       </c>
       <c r="B35" s="3">
-        <v>46142</v>
+        <v>46155</v>
       </c>
       <c r="C35" s="4">
-        <v>4058.99</v>
+        <v>2883.98</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -934,10 +1072,516 @@
         <v>37</v>
       </c>
       <c r="B36" s="3">
+        <v>46155</v>
+      </c>
+      <c r="C36" s="4">
+        <v>4148.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="3">
+        <v>46155</v>
+      </c>
+      <c r="C37" s="4">
+        <v>2783.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="3">
+        <v>46155</v>
+      </c>
+      <c r="C38" s="4">
+        <v>2848.99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="3">
+        <v>46156</v>
+      </c>
+      <c r="C39" s="4">
+        <v>2579.09</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="3">
+        <v>46157</v>
+      </c>
+      <c r="C40" s="4">
+        <v>3599.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="3">
+        <v>46155</v>
+      </c>
+      <c r="C41" s="4">
+        <v>2808.99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="3">
+        <v>46157</v>
+      </c>
+      <c r="C42" s="4">
+        <v>2783.99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="3">
+        <v>46157</v>
+      </c>
+      <c r="C43" s="4">
+        <v>2778.99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="3">
+        <v>46160</v>
+      </c>
+      <c r="C44" s="4">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="3">
+        <v>46162</v>
+      </c>
+      <c r="C45" s="4">
+        <v>2429.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="3">
+        <v>46162</v>
+      </c>
+      <c r="C46" s="4">
+        <v>3684.09</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="3">
+        <v>46162</v>
+      </c>
+      <c r="C47" s="4">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="3">
+        <v>46162</v>
+      </c>
+      <c r="C48" s="4">
+        <v>4658.99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="3">
+        <v>46161</v>
+      </c>
+      <c r="C49" s="4">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="3">
+        <v>46163</v>
+      </c>
+      <c r="C50" s="4">
+        <v>3599.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="3">
+        <v>46163</v>
+      </c>
+      <c r="C51" s="4">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="3">
+        <v>46164</v>
+      </c>
+      <c r="C52" s="4">
+        <v>2808.99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C53" s="4">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="3">
+        <v>46170</v>
+      </c>
+      <c r="C54" s="4">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C55" s="4">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C56" s="4">
+        <v>2998.97</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C57" s="4">
+        <v>2848.99</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C58" s="4">
+        <v>2748.99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C59" s="2">
+        <v>109.99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" s="3">
+        <v>46170</v>
+      </c>
+      <c r="C60" s="4">
+        <v>2918.97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="3">
+        <v>46124</v>
+      </c>
+      <c r="C61" s="4">
+        <v>2024.25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" s="3">
+        <v>46128</v>
+      </c>
+      <c r="C62" s="4">
+        <v>4192.4799999999996</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63" s="3">
+        <v>46129</v>
+      </c>
+      <c r="C63" s="4">
+        <v>3199.47</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B64" s="3">
+        <v>46132</v>
+      </c>
+      <c r="C64" s="4">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" s="3">
+        <v>46130</v>
+      </c>
+      <c r="C65" s="4">
+        <v>8997.75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" s="3">
+        <v>46132</v>
+      </c>
+      <c r="C66" s="4">
+        <v>11021.99</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" s="3">
+        <v>46140</v>
+      </c>
+      <c r="C67" s="4">
+        <v>4083.99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" s="3">
+        <v>46141</v>
+      </c>
+      <c r="C68" s="4">
+        <v>4083.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69" s="3">
+        <v>46141</v>
+      </c>
+      <c r="C69" s="4">
+        <v>2783.99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" s="3">
+        <v>46142</v>
+      </c>
+      <c r="C70" s="4">
+        <v>4058.99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="3">
+        <v>46143</v>
+      </c>
+      <c r="C71" s="4">
+        <v>2783.99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" s="3">
+        <v>46152</v>
+      </c>
+      <c r="C72" s="4">
+        <v>5023.49</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" s="3">
+        <v>46153</v>
+      </c>
+      <c r="C73" s="4">
+        <v>6072.73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" s="3">
+        <v>46155</v>
+      </c>
+      <c r="C74" s="4">
+        <v>2024.24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" s="3">
+        <v>46157</v>
+      </c>
+      <c r="C75" s="4">
+        <v>3684.09</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="3">
+        <v>46160</v>
+      </c>
+      <c r="C76" s="4">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77" s="3">
+        <v>46156</v>
+      </c>
+      <c r="C77" s="4">
+        <v>4083.99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" s="3">
+        <v>46158</v>
+      </c>
+      <c r="C78" s="4">
+        <v>2999.25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" s="3">
+        <v>46160</v>
+      </c>
+      <c r="C79" s="4">
+        <v>2999.25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="3">
+        <v>46162</v>
+      </c>
+      <c r="C80" s="4">
+        <v>2024.24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81" s="3">
+        <v>46163</v>
+      </c>
+      <c r="C81" s="4">
+        <v>2999.25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" s="3">
         <v>46137</v>
       </c>
-      <c r="C36" s="4">
-        <v>8942.19</v>
+      <c r="C82" s="4">
+        <v>4858.2</v>
       </c>
     </row>
   </sheetData>
